--- a/tests/fixtures/canevas_encaissements_demo.xlsx
+++ b/tests/fixtures/canevas_encaissements_demo.xlsx
@@ -401,19 +401,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Client</v>
+        <v>Client *</v>
       </c>
       <c r="B1" t="str">
-        <v>Date encaissement</v>
+        <v>Date encaissement *</v>
       </c>
       <c r="C1" t="str">
-        <v>Montant (DH)</v>
+        <v>Montant (DH) *</v>
       </c>
       <c r="D1" t="str">
         <v>Mode</v>
       </c>
       <c r="E1" t="str">
-        <v>Référence</v>
+        <v>Référence *</v>
       </c>
       <c r="F1" t="str">
         <v>Motif</v>
